--- a/data/trans_orig/IQ23_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ23_R2-Provincia-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>521</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16731</t>
+          <t>16801</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4730</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14054</t>
+          <t>13841</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14069</t>
+          <t>14641</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27989</t>
+          <t>27502</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,38%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35034</t>
+          <t>35161</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44580</t>
+          <t>44813</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44799</t>
+          <t>45137</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54484</t>
+          <t>54738</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>83018</t>
+          <t>83254</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>97048</t>
+          <t>96744</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>85,78%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>3086</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10786</t>
+          <t>10432</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8250</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6084</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15441</t>
+          <t>16047</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28937</t>
+          <t>29028</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>44968</t>
+          <t>44624</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23676</t>
+          <t>24024</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39074</t>
+          <t>39180</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>56942</t>
+          <t>57551</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>78832</t>
+          <t>79673</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50737</t>
+          <t>50493</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66831</t>
+          <t>66527</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65567</t>
+          <t>65086</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81017</t>
+          <t>81200</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121647</t>
+          <t>120228</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>143995</t>
+          <t>143487</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,22%</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4441</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3873</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>7170</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17489</t>
+          <t>17388</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19508</t>
+          <t>19934</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19083</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33846</t>
+          <t>33022</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>23,94%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50108</t>
+          <t>50209</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60453</t>
+          <t>60427</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49500</t>
+          <t>49551</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60172</t>
+          <t>59598</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>103255</t>
+          <t>103702</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>118109</t>
+          <t>118569</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,97%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>522</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>15927</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>8592</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19937</t>
+          <t>19673</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16618</t>
+          <t>17408</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31899</t>
+          <t>31905</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57284</t>
+          <t>57528</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>67172</t>
+          <t>67442</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>57945</t>
+          <t>58474</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69894</t>
+          <t>69793</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>119724</t>
+          <t>119675</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>135269</t>
+          <t>134643</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,45%</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16261</t>
+          <t>16527</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9056</t>
+          <t>9079</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18873</t>
+          <t>19063</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>18599</t>
+          <t>18921</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>32769</t>
+          <t>32372</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,34%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25591</t>
+          <t>25325</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34672</t>
+          <t>34933</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23989</t>
+          <t>24383</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34448</t>
+          <t>34452</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52793</t>
+          <t>52548</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>66959</t>
+          <t>66362</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>76,55%</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13683</t>
+          <t>13741</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5463</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13956</t>
+          <t>14293</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12329</t>
+          <t>11924</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24776</t>
+          <t>23994</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41521</t>
+          <t>41665</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>50708</t>
+          <t>50596</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>45134</t>
+          <t>44847</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>53829</t>
+          <t>53740</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>89761</t>
+          <t>90850</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>102425</t>
+          <t>102987</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,94%</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5198</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>21190</t>
+          <t>20655</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>36921</t>
+          <t>36153</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>23903</t>
+          <t>24161</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>40279</t>
+          <t>39779</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>49115</t>
+          <t>48191</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>72557</t>
+          <t>70709</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>91701</t>
+          <t>92469</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>107432</t>
+          <t>107967</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>92636</t>
+          <t>93363</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>109518</t>
+          <t>109969</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>190119</t>
+          <t>191290</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>213375</t>
+          <t>214335</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>81,1%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>2954</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>10559</t>
+          <t>10424</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6268</t>
+          <t>6258</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>14390</t>
+          <t>13707</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>37607</t>
+          <t>37438</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>55437</t>
+          <t>55936</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>41922</t>
+          <t>42361</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>60924</t>
+          <t>60243</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>84903</t>
+          <t>86135</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>109909</t>
+          <t>110218</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,23%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>90377</t>
+          <t>90570</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>108602</t>
+          <t>109160</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>97213</t>
+          <t>97659</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>116079</t>
+          <t>115890</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>194327</t>
+          <t>193033</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>220429</t>
+          <t>218653</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>69,89%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>8796</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>20927</t>
+          <t>20996</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>9022</t>
+          <t>9016</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>21127</t>
+          <t>21544</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>20730</t>
+          <t>20883</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>37295</t>
+          <t>38157</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>146738</t>
+          <t>146346</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>182586</t>
+          <t>182479</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>154862</t>
+          <t>155237</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>191573</t>
+          <t>191514</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>312048</t>
+          <t>310892</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>362266</t>
+          <t>362724</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,01%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>477467</t>
+          <t>478826</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>514381</t>
+          <t>515681</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>511759</t>
+          <t>513998</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>550048</t>
+          <t>550329</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1003068</t>
+          <t>1002908</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1055854</t>
+          <t>1055340</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,67%</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>799</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8090</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19691</t>
+          <t>20521</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32234</t>
+          <t>33217</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17424</t>
+          <t>17714</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30007</t>
+          <t>30266</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41427</t>
+          <t>39794</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58875</t>
+          <t>57904</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>47,37%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24802</t>
+          <t>23712</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37109</t>
+          <t>36379</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32216</t>
+          <t>31858</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45315</t>
+          <t>45080</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>60698</t>
+          <t>61421</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>78700</t>
+          <t>79510</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>65,05%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7799</t>
+          <t>8022</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11946</t>
+          <t>11806</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>6258</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15845</t>
+          <t>16288</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21113</t>
+          <t>20734</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36187</t>
+          <t>35851</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16323</t>
+          <t>16647</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30613</t>
+          <t>30345</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>41345</t>
+          <t>41490</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>61380</t>
+          <t>60408</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63530</t>
+          <t>63641</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79719</t>
+          <t>79447</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73879</t>
+          <t>73504</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89119</t>
+          <t>88764</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>143661</t>
+          <t>142680</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>163982</t>
+          <t>163459</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,96%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>626</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>671</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>4353</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13428</t>
+          <t>13632</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9156</t>
+          <t>9003</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20085</t>
+          <t>19773</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15763</t>
+          <t>16189</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29994</t>
+          <t>29963</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,61%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51498</t>
+          <t>50468</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61134</t>
+          <t>61151</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48421</t>
+          <t>49220</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60215</t>
+          <t>60404</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>104632</t>
+          <t>104674</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>119473</t>
+          <t>118630</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>85,56%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>796</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7273</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>663</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2639</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11103</t>
+          <t>10984</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12706</t>
+          <t>12728</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24943</t>
+          <t>24689</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13032</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>25570</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28180</t>
+          <t>28390</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45349</t>
+          <t>46326</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>29,08%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49475</t>
+          <t>49706</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62340</t>
+          <t>62508</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>53227</t>
+          <t>53150</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66293</t>
+          <t>66097</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>107214</t>
+          <t>106915</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>126263</t>
+          <t>125533</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>78,79%</t>
         </is>
       </c>
     </row>
@@ -6897,12 +6897,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>726</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6085</t>
+          <t>6650</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>746</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7482</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22662</t>
+          <t>22754</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12400</t>
+          <t>12440</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23485</t>
+          <t>23711</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>26309</t>
+          <t>27094</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>42261</t>
+          <t>42454</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,83%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19467</t>
+          <t>18868</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30898</t>
+          <t>30304</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22266</t>
+          <t>22217</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33429</t>
+          <t>33497</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>45337</t>
+          <t>44428</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60881</t>
+          <t>60514</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>66,75%</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>701</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4607</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12900</t>
+          <t>12743</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10792</t>
+          <t>11047</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21950</t>
+          <t>22212</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17418</t>
+          <t>17769</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31901</t>
+          <t>31872</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41503</t>
+          <t>42204</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>50693</t>
+          <t>50807</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>36386</t>
+          <t>36154</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>48306</t>
+          <t>47907</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>80966</t>
+          <t>81271</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>96792</t>
+          <t>96410</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>82,95%</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9893</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>22182</t>
+          <t>22308</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>38721</t>
+          <t>37601</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>26531</t>
+          <t>26816</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>43958</t>
+          <t>44327</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>51732</t>
+          <t>52702</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>76795</t>
+          <t>76651</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>98370</t>
+          <t>98615</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>114964</t>
+          <t>114896</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>98425</t>
+          <t>97984</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>116182</t>
+          <t>115752</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>201326</t>
+          <t>202111</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>226807</t>
+          <t>226590</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,84%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>625</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6199</t>
+          <t>6837</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>653</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>6553</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10235</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>37882</t>
+          <t>37535</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>56630</t>
+          <t>56919</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>35739</t>
+          <t>37235</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>55019</t>
+          <t>54746</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>78423</t>
+          <t>79662</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>105591</t>
+          <t>106759</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,77%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>105898</t>
+          <t>105283</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>124676</t>
+          <t>124775</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>112264</t>
+          <t>113898</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>132443</t>
+          <t>131903</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>224333</t>
+          <t>224533</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>252012</t>
+          <t>251132</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,74%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>11417</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>25823</t>
+          <t>24964</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>15187</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>29831</t>
+          <t>31094</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>30103</t>
+          <t>29396</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>51410</t>
+          <t>50495</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>162579</t>
+          <t>161945</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>200260</t>
+          <t>200562</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>172062</t>
+          <t>173928</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>212520</t>
+          <t>214090</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>343734</t>
+          <t>345473</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>398703</t>
+          <t>402882</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,56%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>490168</t>
+          <t>491483</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>529356</t>
+          <t>531483</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>517703</t>
+          <t>516931</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>559539</t>
+          <t>557348</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1022475</t>
+          <t>1019954</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1079630</t>
+          <t>1078025</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,73%</t>
         </is>
       </c>
     </row>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>2498</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17271</t>
+          <t>16752</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28824</t>
+          <t>28445</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21255</t>
+          <t>19894</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34310</t>
+          <t>33427</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40829</t>
+          <t>41201</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58727</t>
+          <t>59631</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,94%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28476</t>
+          <t>28386</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39801</t>
+          <t>40103</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30152</t>
+          <t>31035</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43207</t>
+          <t>44568</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>62654</t>
+          <t>61367</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>80831</t>
+          <t>80087</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>65,73%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7227</t>
+          <t>6556</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13006</t>
+          <t>13502</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33757</t>
+          <t>33391</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49728</t>
+          <t>50083</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34802</t>
+          <t>34015</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>52081</t>
+          <t>52048</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>73016</t>
+          <t>73363</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>96904</t>
+          <t>96960</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,51%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48075</t>
+          <t>47748</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64829</t>
+          <t>64705</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54411</t>
+          <t>55242</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72387</t>
+          <t>72242</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>108205</t>
+          <t>107586</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132253</t>
+          <t>132057</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,98%</t>
         </is>
       </c>
     </row>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21957</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35548</t>
+          <t>36411</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21983</t>
+          <t>22233</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34924</t>
+          <t>35225</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47989</t>
+          <t>48303</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67437</t>
+          <t>67206</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>49,92%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29468</t>
+          <t>28550</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43589</t>
+          <t>42852</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33593</t>
+          <t>33292</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46534</t>
+          <t>46284</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67188</t>
+          <t>66748</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>86570</t>
+          <t>85806</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>63,74%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>581</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7597</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1689</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13469</t>
+          <t>13418</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25640</t>
+          <t>25624</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19147</t>
+          <t>20009</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33847</t>
+          <t>34379</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35763</t>
+          <t>36774</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55168</t>
+          <t>55068</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,82%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48217</t>
+          <t>48091</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>61058</t>
+          <t>61180</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>45984</t>
+          <t>45855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>60785</t>
+          <t>60160</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>98692</t>
+          <t>98173</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>118391</t>
+          <t>116957</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>73,96%</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3087</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10644</t>
+          <t>10584</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11865</t>
+          <t>12540</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8975</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>20235</t>
+          <t>20207</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -11463,12 +11463,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32794</t>
+          <t>32854</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40283</t>
+          <t>40351</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34485</t>
+          <t>33810</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42383</t>
+          <t>42428</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>69553</t>
+          <t>69581</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80813</t>
+          <t>81055</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,27%</t>
         </is>
       </c>
     </row>
@@ -11733,7 +11733,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11738</t>
+          <t>11693</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22625</t>
+          <t>22798</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10587</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21412</t>
+          <t>22369</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>24528</t>
+          <t>24940</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41087</t>
+          <t>41583</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>37,12%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31648</t>
+          <t>31475</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42535</t>
+          <t>42580</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>35337</t>
+          <t>34615</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>46537</t>
+          <t>46693</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>70369</t>
+          <t>69185</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>86925</t>
+          <t>86472</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,2%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>584</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>5911</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2558</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10194</t>
+          <t>9723</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4206</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12794</t>
+          <t>13095</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29778</t>
+          <t>29910</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>46090</t>
+          <t>47629</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>35664</t>
+          <t>35527</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>53639</t>
+          <t>53755</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>70897</t>
+          <t>69742</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>94611</t>
+          <t>94676</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,64%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>88304</t>
+          <t>87947</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>105387</t>
+          <t>105068</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>85425</t>
+          <t>84801</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>103726</t>
+          <t>103669</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>179432</t>
+          <t>178835</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>203440</t>
+          <t>204779</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,76%</t>
         </is>
       </c>
     </row>
@@ -12610,7 +12610,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12625,7 +12625,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12645,7 +12645,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>525</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12695,7 +12695,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>26153</t>
+          <t>26759</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>42106</t>
+          <t>42041</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>32178</t>
+          <t>32602</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>50466</t>
+          <t>49368</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>62188</t>
+          <t>63073</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>86486</t>
+          <t>86839</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>117701</t>
+          <t>117401</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>133691</t>
+          <t>133357</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>113636</t>
+          <t>115535</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>132283</t>
+          <t>132575</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>237850</t>
+          <t>238045</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>262199</t>
+          <t>262180</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>7578</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>18865</t>
+          <t>19089</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>6835</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>18438</t>
+          <t>17898</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>16830</t>
+          <t>16195</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>31855</t>
+          <t>31552</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>186700</t>
+          <t>188877</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>225389</t>
+          <t>226691</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>212308</t>
+          <t>212559</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>253233</t>
+          <t>254974</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>414722</t>
+          <t>412495</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>472665</t>
+          <t>468156</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,57%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>461446</t>
+          <t>458336</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>500446</t>
+          <t>497620</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>474082</t>
+          <t>472693</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>515200</t>
+          <t>515355</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>939878</t>
+          <t>945678</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>999255</t>
+          <t>1002204</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,72%</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13808,7 +13808,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>481</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -13866,12 +13866,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>8576</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20594</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13881,12 +13881,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15752</t>
+          <t>14879</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30026</t>
+          <t>29480</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26029</t>
+          <t>27556</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46248</t>
+          <t>46148</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,23%</t>
         </is>
       </c>
     </row>
@@ -13979,12 +13979,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50887</t>
+          <t>51377</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>63523</t>
+          <t>64099</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49116</t>
+          <t>49643</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63142</t>
+          <t>64077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14029,12 +14029,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>105104</t>
+          <t>104673</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>125363</t>
+          <t>123597</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>80,97%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>803</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>9136</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>404</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11675</t>
+          <t>11861</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16152</t>
+          <t>15799</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10535</t>
+          <t>11327</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33438</t>
+          <t>33811</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28418</t>
+          <t>27171</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48097</t>
+          <t>47934</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>41209</t>
+          <t>40901</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>74568</t>
+          <t>74448</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89161</t>
+          <t>88372</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>114062</t>
+          <t>112654</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75754</t>
+          <t>75201</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96337</t>
+          <t>96552</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>170718</t>
+          <t>170104</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>208312</t>
+          <t>206366</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>81,5%</t>
         </is>
       </c>
     </row>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19809</t>
+          <t>19368</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31476</t>
+          <t>31301</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,12 +14793,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19209</t>
+          <t>19177</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31661</t>
+          <t>32724</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42440</t>
+          <t>41956</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58895</t>
+          <t>59373</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,33%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26792</t>
+          <t>26967</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38459</t>
+          <t>38900</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34867</t>
+          <t>33836</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>47210</t>
+          <t>47094</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>65507</t>
+          <t>64935</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>82387</t>
+          <t>82546</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,81%</t>
         </is>
       </c>
     </row>
@@ -15126,7 +15126,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15161,7 +15161,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>5686</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15196,7 +15196,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>7443</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15211,7 +15211,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>8890</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20524</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9656</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25791</t>
+          <t>27075</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21603</t>
+          <t>20880</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41417</t>
+          <t>42215</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,77%</t>
         </is>
       </c>
     </row>
@@ -15347,12 +15347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44409</t>
+          <t>44837</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>56022</t>
+          <t>55966</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49409</t>
+          <t>48614</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66195</t>
+          <t>66401</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15397,12 +15397,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>98514</t>
+          <t>97963</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>118881</t>
+          <t>119367</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>84,16%</t>
         </is>
       </c>
     </row>
@@ -15690,12 +15690,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>5448</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12393</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9922</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10651</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>20020</t>
+          <t>20225</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,88%</t>
         </is>
       </c>
     </row>
@@ -15803,12 +15803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22120</t>
+          <t>22266</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29121</t>
+          <t>29065</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30797</t>
+          <t>30355</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37250</t>
+          <t>37445</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55212</t>
+          <t>55007</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>64581</t>
+          <t>65033</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15888,12 +15888,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>86,44%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12614</t>
+          <t>12934</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22550</t>
+          <t>22788</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20311</t>
+          <t>20321</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32601</t>
+          <t>32445</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>36408</t>
+          <t>36457</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>52855</t>
+          <t>51925</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>50,73%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>23617</t>
+          <t>23379</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>33553</t>
+          <t>33233</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>23585</t>
+          <t>23741</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>35875</t>
+          <t>35865</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>49498</t>
+          <t>50428</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>65945</t>
+          <t>65896</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,38%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>764</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6901</t>
+          <t>6222</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16529,7 +16529,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16544,7 +16544,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>823</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8620</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>49472</t>
+          <t>49108</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>68586</t>
+          <t>68959</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>54590</t>
+          <t>54601</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>82087</t>
+          <t>80596</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>109118</t>
+          <t>109142</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>143054</t>
+          <t>141963</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>50,61%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>53519</t>
+          <t>52912</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>73273</t>
+          <t>72945</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>73386</t>
+          <t>74511</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>100801</t>
+          <t>100606</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>133156</t>
+          <t>135282</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>168077</t>
+          <t>167804</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,82%</t>
         </is>
       </c>
     </row>
@@ -16950,7 +16950,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5050</t>
+          <t>5683</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16965,7 +16965,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16985,7 +16985,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>657</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6932</t>
+          <t>6878</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17035,7 +17035,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>14599</t>
+          <t>14894</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>28065</t>
+          <t>28783</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>13640</t>
+          <t>13544</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>27518</t>
+          <t>27813</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>31925</t>
+          <t>32114</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>51513</t>
+          <t>50925</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>102249</t>
+          <t>101404</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>116053</t>
+          <t>115708</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>127760</t>
+          <t>128077</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>142532</t>
+          <t>142283</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>234042</t>
+          <t>234439</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>254093</t>
+          <t>254372</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,2%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>4474</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>14902</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>3613</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>17103</t>
+          <t>18565</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>10260</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>26964</t>
+          <t>27234</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>154090</t>
+          <t>156452</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>204120</t>
+          <t>203213</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>199124</t>
+          <t>198071</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>247200</t>
+          <t>247350</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>368954</t>
+          <t>369573</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>440360</t>
+          <t>434975</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,64%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>447035</t>
+          <t>447861</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>496594</t>
+          <t>495758</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>503401</t>
+          <t>504217</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>552053</t>
+          <t>554632</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>963471</t>
+          <t>967512</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1034488</t>
+          <t>1032773</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,75%</t>
         </is>
       </c>
     </row>
